--- a/data_input/housing_type_emissions.xlsx
+++ b/data_input/housing_type_emissions.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data_input/housing_type_emissions.xlsx
+++ b/data_input/housing_type_emissions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,16 +458,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>decile 1 (poorest)</t>
+          <t>owner occupied</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>row house</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3172.816648435105</v>
+        <v>4373.101803628062</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -475,13 +475,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7400.557048481546</v>
+        <v>6131.060106300586</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>decile 10 (richest)</t>
+          <t>priate rental</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6654.656875677243</v>
+        <v>5009.870707331612</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8297.961457116206</v>
+        <v>10013.3054092583</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>decile 2</t>
+          <t>social rental</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3572.620915837489</v>
+        <v>3199.561388576356</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -521,168 +521,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6008.748103530121</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>decile 3</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>row house</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>3790.279156666922</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>detached</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>5993.623860226122</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>decile 4</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>row house</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>4020.058879018074</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>detached</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>5971.960206611907</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>decile 5</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>row house</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>4126.931786533699</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>detached</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5808.621501919441</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>decile 6</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>row house</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>4404.623013532689</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>detached</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6068.064522204058</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>decile 7</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>row house</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>4553.626339879565</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>detached</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>5969.937107495742</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>decile 8</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>row house</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>5119.166590122389</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>detached</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>6856.358767467361</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>decile 9</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>multifamily</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>5743.500263518989</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>detached</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>7282.177968137723</v>
+        <v>6182.582527589786</v>
       </c>
     </row>
   </sheetData>

--- a/data_input/housing_type_emissions.xlsx
+++ b/data_input/housing_type_emissions.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4373.101803628062</v>
+        <v>3843.270102828446</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6131.060106300586</v>
+        <v>5215.223206488878</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5009.870707331612</v>
+        <v>4076.25660536549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10013.3054092583</v>
+        <v>6907.512752388069</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3199.561388576356</v>
+        <v>2804.220003152369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6182.582527589786</v>
+        <v>5589.000625223216</v>
       </c>
     </row>
   </sheetData>

--- a/data_input/housing_type_emissions.xlsx
+++ b/data_input/housing_type_emissions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>owner occupied</t>
+          <t>51-90%</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3843.270102828446</v>
+        <v>3604.955779118386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -475,13 +475,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5215.223206488878</v>
+        <v>4700.759253187494</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>priate rental</t>
+          <t>91-99%</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4076.25660536549</v>
+        <v>4349.489988316975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6907.512752388069</v>
+        <v>5590.795231924177</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>social rental</t>
+          <t>poorest 50%</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2804.220003152369</v>
+        <v>2930.936763717956</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -521,7 +521,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5589.000625223216</v>
+        <v>4687.258071440809</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>top 1%</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>detached</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>6454.860757007323</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>multifamily</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>7345.512812568913</v>
       </c>
     </row>
   </sheetData>

--- a/data_input/housing_type_emissions.xlsx
+++ b/data_input/housing_type_emissions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>51-90%</t>
+          <t>decile 1 (poorest)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3604.955779118386</v>
+        <v>2399.443121400958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -475,13 +475,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4700.759253187494</v>
+        <v>4874.07729377526</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>91-99%</t>
+          <t>decile 10 (richest)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4349.489988316975</v>
+        <v>4486.178766995059</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5590.795231924177</v>
+        <v>5701.901656362323</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>poorest 50%</t>
+          <t>decile 2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2930.936763717956</v>
+        <v>2832.017746713345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -521,30 +521,168 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4687.258071440809</v>
+        <v>4315.230129792112</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>top 1%</t>
+          <t>decile 3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>detached</t>
+          <t>row house</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6454.860757007323</v>
+        <v>2848.158899408218</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>detached</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>7345.512812568913</v>
+        <v>4310.881078094211</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>decile 4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>row house</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3142.050934978702</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>detached</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4757.787279965484</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>decile 5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>row house</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3195.597811098685</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>detached</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5081.368473628407</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>decile 6</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>row house</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3157.750757816998</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>detached</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4564.123594698536</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>decile 7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>row house</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3475.414898114308</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>detached</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4471.282604865744</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>decile 8</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>row house</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3917.343949707717</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>detached</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4901.02922312752</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>decile 9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>row house</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3832.413384388308</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>detached</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4875.145381802827</v>
       </c>
     </row>
   </sheetData>

--- a/data_input/housing_type_emissions.xlsx
+++ b/data_input/housing_type_emissions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>decile 1 (poorest)</t>
+          <t>owner occupied</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2399.443121400958</v>
+        <v>3843.270102828446</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -475,13 +475,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4874.07729377526</v>
+        <v>5215.223206488878</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>decile 10 (richest)</t>
+          <t>private rental</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4486.178766995059</v>
+        <v>4076.25660536549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5701.901656362323</v>
+        <v>6907.512752388069</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>decile 2</t>
+          <t>social rental</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2832.017746713345</v>
+        <v>2804.220003152369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -521,168 +521,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4315.230129792112</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>decile 3</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>row house</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2848.158899408218</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>detached</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>4310.881078094211</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>decile 4</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>row house</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>3142.050934978702</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>detached</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>4757.787279965484</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>decile 5</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>row house</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>3195.597811098685</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>detached</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5081.368473628407</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>decile 6</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>row house</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3157.750757816998</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>detached</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>4564.123594698536</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>decile 7</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>row house</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>3475.414898114308</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>detached</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>4471.282604865744</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>decile 8</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>row house</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>3917.343949707717</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>detached</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>4901.02922312752</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>decile 9</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>row house</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>3832.413384388308</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>detached</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>4875.145381802827</v>
+        <v>5589.000625223216</v>
       </c>
     </row>
   </sheetData>

--- a/data_input/housing_type_emissions.xlsx
+++ b/data_input/housing_type_emissions.xlsx
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3843.270102828446</v>
+        <v>3892.803866556672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5215.223206488878</v>
+        <v>5336.426984815058</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4076.25660536549</v>
+        <v>4394.400806936712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6907.512752388069</v>
+        <v>7101.198283876248</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2804.220003152369</v>
+        <v>3007.913493479257</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5589.000625223216</v>
+        <v>5577.366453637566</v>
       </c>
     </row>
   </sheetData>

--- a/data_input/housing_type_emissions.xlsx
+++ b/data_input/housing_type_emissions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>owner occupied</t>
+          <t>51-90%</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3892.803866556672</v>
+        <v>3670.740432778579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -475,13 +475,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5336.426984815058</v>
+        <v>4807.78441576897</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>private rental</t>
+          <t>91-99%</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4394.400806936712</v>
+        <v>4414.13796494234</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>7101.198283876248</v>
+        <v>5674.012524609706</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>social rental</t>
+          <t>poorest 50%</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3007.913493479257</v>
+        <v>3028.149045466095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -521,7 +521,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5577.366453637566</v>
+        <v>4907.209568538062</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>top 1%</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>multifamily</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>6724.296686248756</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>row house</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6868.265980251309</v>
       </c>
     </row>
   </sheetData>
